--- a/Juhayna-Dashboard-Master-Data.xlsx
+++ b/Juhayna-Dashboard-Master-Data.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,15 +12,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot-Rent Route Master" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Master" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spot-Rent Route Master'!$A$3:$G$3</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,24 +33,24 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000C3B72"/>
+      <color rgb="FF0C3B72"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00333333"/>
+      <color rgb="FF333333"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000C3B72"/>
+      <color rgb="FF0C3B72"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -59,11 +60,18 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00B8860B"/>
+      <color rgb="FFB8860B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,12 +80,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000C3B72"/>
+        <fgColor rgb="FF0C3B72"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,23 +114,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D8DDE6"/>
+        <color rgb="FFD8DDE6"/>
       </left>
       <right style="thin">
-        <color rgb="00D8DDE6"/>
+        <color rgb="FFD8DDE6"/>
       </right>
       <top style="thin">
-        <color rgb="00D8DDE6"/>
+        <color rgb="FFD8DDE6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D8DDE6"/>
+        <color rgb="FFD8DDE6"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,9 +144,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -485,13 +519,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>JUHAYNA DASHBOARD — CONSOLIDATED MASTER DATA v1</t>
@@ -499,7 +533,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -516,7 +550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -554,12 +588,40 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Yellow cells = to be edited/validated by the team. Adding a row anywhere is enough — the dashboard reads whole columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>UPDATE (heavy-fleet price list merge):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Green = spot rate taken from the Heavy Fleet price list. Price-list zeros mean 'not quoted' — current rate kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Orange = route weight was missing → set to 1 day. Validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Blue italic = EXTRAPOLATED value (RT km in Spot-Rent Route Master; missing incentives in Owned Route Master). Method in the Comment / Distance basis column. Replace with actuals when known.</t>
         </is>
       </c>
     </row>
@@ -575,23 +637,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E216"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>OWNED ROUTE MASTER</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Route Name</t>
@@ -701,13 +762,15 @@
       <c r="B8" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="14" t="n">
+        <v>165</v>
+      </c>
       <c r="D8" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -740,10 +803,12 @@
       <c r="C10" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D10" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -878,10 +943,12 @@
       <c r="C18" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D18" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -897,10 +964,12 @@
       <c r="C19" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D19" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1001,10 +1070,12 @@
       <c r="C25" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D25" s="14" t="n">
+        <v>235</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1091,12 @@
       <c r="C26" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D26" s="14" t="n">
+        <v>235</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1056,10 +1129,12 @@
       <c r="C28" s="5" t="n">
         <v>260</v>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D28" s="14" t="n">
+        <v>325</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1075,10 +1150,12 @@
       <c r="C29" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D29" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1188,12 @@
       <c r="C31" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D31" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1209,12 @@
       <c r="C32" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D32" s="14" t="n">
+        <v>260</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1183,10 +1264,12 @@
       <c r="C35" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D35" s="14" t="n">
+        <v>620</v>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1219,10 +1302,12 @@
       <c r="C37" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D37" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1238,10 +1323,12 @@
       <c r="C38" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D38" s="14" t="n">
+        <v>235</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1325,10 +1412,12 @@
       <c r="C43" s="5" t="n">
         <v>520</v>
       </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D43" s="14" t="n">
+        <v>645</v>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1430,15 @@
       <c r="B44" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C44" s="6" t="n"/>
+      <c r="C44" s="14" t="n">
+        <v>620</v>
+      </c>
       <c r="D44" s="5" t="n">
         <v>770</v>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1397,10 +1488,12 @@
       <c r="C47" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D47" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1430,13 +1523,15 @@
       <c r="B49" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C49" s="6" t="n"/>
+      <c r="C49" s="14" t="n">
+        <v>165</v>
+      </c>
       <c r="D49" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1486,10 +1581,12 @@
       <c r="C52" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D52" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1502,11 +1599,15 @@
       <c r="B53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C53" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1654,15 @@
       <c r="B56" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C56" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1570,11 +1675,15 @@
       <c r="B57" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C57" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1604,13 +1713,15 @@
       <c r="B59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="6" t="n"/>
+      <c r="C59" s="14" t="n">
+        <v>310</v>
+      </c>
       <c r="D59" s="5" t="n">
         <v>388</v>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1626,10 +1737,12 @@
       <c r="C60" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D60" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1662,10 +1775,12 @@
       <c r="C62" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D62" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1712,13 +1827,15 @@
       <c r="B65" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C65" s="6" t="n"/>
+      <c r="C65" s="14" t="n">
+        <v>565</v>
+      </c>
       <c r="D65" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1868,12 @@
       <c r="C67" s="5" t="n">
         <v>195</v>
       </c>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D67" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1787,10 +1906,12 @@
       <c r="C69" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D69" s="14" t="n">
+        <v>310</v>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1803,11 +1924,15 @@
       <c r="B70" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C70" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1837,11 +1962,15 @@
       <c r="B72" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C72" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1922,13 +2051,15 @@
       <c r="B77" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C77" s="6" t="n"/>
+      <c r="C77" s="14" t="n">
+        <v>530</v>
+      </c>
       <c r="D77" s="5" t="n">
         <v>658</v>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1941,11 +2072,15 @@
       <c r="B78" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="n"/>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C78" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>710</v>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-2.5 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1961,10 +2096,12 @@
       <c r="C79" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="D79" s="6" t="n"/>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D79" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -1977,13 +2114,15 @@
       <c r="B80" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="6" t="n"/>
+      <c r="C80" s="14" t="n">
+        <v>295</v>
+      </c>
       <c r="D80" s="5" t="n">
         <v>367</v>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -1996,11 +2135,15 @@
       <c r="B81" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C81" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2016,10 +2159,12 @@
       <c r="C82" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D82" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2035,10 +2180,12 @@
       <c r="C83" s="5" t="n">
         <v>410</v>
       </c>
-      <c r="D83" s="6" t="n"/>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D83" s="14" t="n">
+        <v>510</v>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2051,13 +2198,15 @@
       <c r="B84" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C84" s="6" t="n"/>
+      <c r="C84" s="14" t="n">
+        <v>465</v>
+      </c>
       <c r="D84" s="5" t="n">
         <v>580</v>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2073,10 +2222,12 @@
       <c r="C85" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D85" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2106,11 +2257,15 @@
       <c r="B87" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C87" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2123,13 +2278,15 @@
       <c r="B88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="6" t="n"/>
+      <c r="C88" s="14" t="n">
+        <v>295</v>
+      </c>
       <c r="D88" s="5" t="n">
         <v>367</v>
       </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2299,15 @@
       <c r="B89" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C89" s="6" t="n"/>
+      <c r="C89" s="14" t="n">
+        <v>145</v>
+      </c>
       <c r="D89" s="5" t="n">
         <v>177</v>
       </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2178,11 +2337,15 @@
       <c r="B91" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6" t="n"/>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C91" s="14" t="n">
+        <v>340</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 4 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2358,15 @@
       <c r="B92" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C92" s="6" t="n"/>
+      <c r="C92" s="14" t="n">
+        <v>765</v>
+      </c>
       <c r="D92" s="5" t="n">
         <v>950</v>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2231,11 +2396,15 @@
       <c r="B94" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C94" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2251,10 +2420,12 @@
       <c r="C95" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D95" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2438,15 @@
       <c r="B96" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C96" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2287,10 +2462,12 @@
       <c r="C97" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D97" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2306,10 +2483,12 @@
       <c r="C98" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D98" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2322,11 +2501,15 @@
       <c r="B99" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C99" s="14" t="n">
+        <v>340</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 4 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2342,10 +2525,12 @@
       <c r="C100" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D100" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2358,11 +2543,15 @@
       <c r="B101" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C101" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2392,13 +2581,15 @@
       <c r="B103" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C103" s="6" t="n"/>
+      <c r="C103" s="14" t="n">
+        <v>415</v>
+      </c>
       <c r="D103" s="5" t="n">
         <v>515</v>
       </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2411,13 +2602,15 @@
       <c r="B104" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C104" s="6" t="n"/>
+      <c r="C104" s="14" t="n">
+        <v>320</v>
+      </c>
       <c r="D104" s="5" t="n">
         <v>398</v>
       </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2433,10 +2626,12 @@
       <c r="C105" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D105" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2469,10 +2664,12 @@
       <c r="C107" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D107" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2485,11 +2682,15 @@
       <c r="B108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C108" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2505,10 +2706,12 @@
       <c r="C109" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D109" s="14" t="n">
+        <v>375</v>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2538,11 +2741,15 @@
       <c r="B111" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C111" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>710</v>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-2.5 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2558,10 +2765,12 @@
       <c r="C112" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D112" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2574,13 +2783,15 @@
       <c r="B113" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C113" s="6" t="n"/>
+      <c r="C113" s="14" t="n">
+        <v>570</v>
+      </c>
       <c r="D113" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2596,10 +2807,12 @@
       <c r="C114" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D114" s="14" t="n">
+        <v>395</v>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2612,11 +2825,15 @@
       <c r="B115" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C115" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>710</v>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-2.5 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2680,11 +2897,15 @@
       <c r="B119" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6" t="n"/>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C119" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2697,11 +2918,15 @@
       <c r="B120" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C120" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2714,11 +2939,15 @@
       <c r="B121" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C121" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2768,10 +2997,12 @@
       <c r="C124" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D124" s="6" t="n"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D124" s="14" t="n">
+        <v>310</v>
+      </c>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2784,11 +3015,15 @@
       <c r="B125" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C125" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E125" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2818,13 +3053,15 @@
       <c r="B127" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C127" s="6" t="n"/>
+      <c r="C127" s="14" t="n">
+        <v>320</v>
+      </c>
       <c r="D127" s="5" t="n">
         <v>398</v>
       </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E127" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -2837,11 +3074,15 @@
       <c r="B128" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C128" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2854,11 +3095,15 @@
       <c r="B129" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C129" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E129" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2874,10 +3119,12 @@
       <c r="C130" s="5" t="n">
         <v>187</v>
       </c>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D130" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="E130" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2924,11 +3171,15 @@
       <c r="B133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C133" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E133" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2941,11 +3192,15 @@
       <c r="B134" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C134" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E134" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2958,11 +3213,15 @@
       <c r="B135" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C135" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E135" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2975,11 +3234,15 @@
       <c r="B136" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C136" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -2995,10 +3258,12 @@
       <c r="C137" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="D137" s="6" t="n"/>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D137" s="14" t="n">
+        <v>455</v>
+      </c>
+      <c r="E137" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3028,11 +3293,15 @@
       <c r="B139" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C139" s="6" t="n"/>
-      <c r="D139" s="6" t="n"/>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C139" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E139" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3062,11 +3331,15 @@
       <c r="B141" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C141" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D141" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3079,11 +3352,15 @@
       <c r="B142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C142" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3096,13 +3373,15 @@
       <c r="B143" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C143" s="6" t="n"/>
+      <c r="C143" s="14" t="n">
+        <v>370</v>
+      </c>
       <c r="D143" s="5" t="n">
         <v>458</v>
       </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E143" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3118,10 +3397,12 @@
       <c r="C144" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D144" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="E144" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3134,13 +3415,15 @@
       <c r="B145" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C145" s="6" t="n"/>
+      <c r="C145" s="14" t="n">
+        <v>295</v>
+      </c>
       <c r="D145" s="5" t="n">
         <v>367</v>
       </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E145" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3153,11 +3436,15 @@
       <c r="B146" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C146" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E146" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3170,13 +3457,15 @@
       <c r="B147" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C147" s="6" t="n"/>
+      <c r="C147" s="14" t="n">
+        <v>515</v>
+      </c>
       <c r="D147" s="5" t="n">
         <v>640</v>
       </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3189,11 +3478,15 @@
       <c r="B148" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C148" s="6" t="n"/>
-      <c r="D148" s="6" t="n"/>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C148" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3209,10 +3502,12 @@
       <c r="C149" s="5" t="n">
         <v>260</v>
       </c>
-      <c r="D149" s="6" t="n"/>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D149" s="14" t="n">
+        <v>325</v>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3225,11 +3520,15 @@
       <c r="B150" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C150" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D150" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3242,11 +3541,15 @@
       <c r="B151" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C151" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="D151" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3262,10 +3565,12 @@
       <c r="C152" s="5" t="n">
         <v>187</v>
       </c>
-      <c r="D152" s="6" t="n"/>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D152" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="E152" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3278,11 +3583,15 @@
       <c r="B153" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C153" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D153" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3295,11 +3604,15 @@
       <c r="B154" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C154" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D154" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E154" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3315,10 +3628,12 @@
       <c r="C155" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D155" s="6" t="n"/>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D155" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3348,13 +3663,15 @@
       <c r="B157" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C157" s="6" t="n"/>
+      <c r="C157" s="14" t="n">
+        <v>465</v>
+      </c>
       <c r="D157" s="5" t="n">
         <v>580</v>
       </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3370,10 +3687,12 @@
       <c r="C158" s="5" t="n">
         <v>380</v>
       </c>
-      <c r="D158" s="6" t="n"/>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D158" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3389,10 +3708,12 @@
       <c r="C159" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D159" s="6" t="n"/>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D159" s="14" t="n">
+        <v>310</v>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3405,11 +3726,15 @@
       <c r="B160" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C160" s="6" t="n"/>
-      <c r="D160" s="6" t="n"/>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C160" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D160" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3422,11 +3747,15 @@
       <c r="B161" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C161" s="6" t="n"/>
-      <c r="D161" s="6" t="n"/>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C161" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D161" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3442,10 +3771,12 @@
       <c r="C162" s="5" t="n">
         <v>172</v>
       </c>
-      <c r="D162" s="6" t="n"/>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D162" s="14" t="n">
+        <v>215</v>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3458,11 +3789,15 @@
       <c r="B163" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C163" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D163" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3478,10 +3813,12 @@
       <c r="C164" s="5" t="n">
         <v>260</v>
       </c>
-      <c r="D164" s="6" t="n"/>
-      <c r="E164" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D164" s="14" t="n">
+        <v>325</v>
+      </c>
+      <c r="E164" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3494,11 +3831,15 @@
       <c r="B165" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C165" s="6" t="n"/>
-      <c r="D165" s="6" t="n"/>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C165" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D165" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E165" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3511,11 +3852,15 @@
       <c r="B166" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C166" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D166" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E166" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3873,15 @@
       <c r="B167" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C167" s="6" t="n"/>
-      <c r="D167" s="6" t="n"/>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C167" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D167" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E167" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3545,11 +3894,15 @@
       <c r="B168" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C168" s="6" t="n"/>
-      <c r="D168" s="6" t="n"/>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C168" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D168" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E168" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3562,11 +3915,15 @@
       <c r="B169" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C169" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D169" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E169" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3579,11 +3936,15 @@
       <c r="B170" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6" t="n"/>
-      <c r="E170" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C170" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D170" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E170" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3599,10 +3960,12 @@
       <c r="C171" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D171" s="6" t="n"/>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D171" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E171" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3615,11 +3978,15 @@
       <c r="B172" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-      <c r="E172" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C172" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D172" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E172" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3632,11 +3999,15 @@
       <c r="B173" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6" t="n"/>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C173" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="D173" s="14" t="n">
+        <v>710</v>
+      </c>
+      <c r="E173" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-2.5 routes; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3649,11 +4020,15 @@
       <c r="B174" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C174" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D174" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3666,11 +4041,15 @@
       <c r="B175" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C175" s="6" t="n"/>
-      <c r="D175" s="6" t="n"/>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C175" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D175" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E175" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3683,11 +4062,15 @@
       <c r="B176" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C176" s="6" t="n"/>
-      <c r="D176" s="6" t="n"/>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C176" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D176" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E176" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3700,11 +4083,15 @@
       <c r="B177" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C177" s="6" t="n"/>
-      <c r="D177" s="6" t="n"/>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C177" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D177" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E177" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3717,11 +4104,15 @@
       <c r="B178" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C178" s="6" t="n"/>
-      <c r="D178" s="6" t="n"/>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C178" s="14" t="n">
+        <v>515</v>
+      </c>
+      <c r="D178" s="14" t="n">
+        <v>640</v>
+      </c>
+      <c r="E178" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = interpolated weight 1.5–2.5; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3734,13 +4125,15 @@
       <c r="B179" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="C179" s="6" t="n"/>
+      <c r="C179" s="14" t="n">
+        <v>570</v>
+      </c>
       <c r="D179" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E179" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3753,11 +4146,15 @@
       <c r="B180" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C180" s="6" t="n"/>
-      <c r="D180" s="6" t="n"/>
-      <c r="E180" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C180" s="14" t="n">
+        <v>205</v>
+      </c>
+      <c r="D180" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E180" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = interpolated weight 0–0.5; double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3770,11 +4167,15 @@
       <c r="B181" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C181" s="6" t="n"/>
-      <c r="D181" s="6" t="n"/>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C181" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D181" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E181" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3790,10 +4191,12 @@
       <c r="C182" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D182" s="6" t="n"/>
-      <c r="E182" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D182" s="14" t="n">
+        <v>260</v>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3806,11 +4209,15 @@
       <c r="B183" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-      <c r="E183" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C183" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="D183" s="14" t="n">
+        <v>485</v>
+      </c>
+      <c r="E183" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3823,11 +4230,15 @@
       <c r="B184" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C184" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D184" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E184" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3843,10 +4254,12 @@
       <c r="C185" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="D185" s="6" t="n"/>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D185" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E185" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3862,10 +4275,12 @@
       <c r="C186" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="D186" s="6" t="n"/>
-      <c r="E186" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D186" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E186" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3878,11 +4293,15 @@
       <c r="B187" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6" t="n"/>
-      <c r="E187" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C187" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D187" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E187" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3898,10 +4317,12 @@
       <c r="C188" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="D188" s="6" t="n"/>
-      <c r="E188" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D188" s="14" t="n">
+        <v>460</v>
+      </c>
+      <c r="E188" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3914,13 +4335,15 @@
       <c r="B189" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C189" s="6" t="n"/>
+      <c r="C189" s="14" t="n">
+        <v>215</v>
+      </c>
       <c r="D189" s="5" t="n">
         <v>268</v>
       </c>
-      <c r="E189" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -3933,11 +4356,15 @@
       <c r="B190" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C190" s="6" t="n"/>
-      <c r="D190" s="6" t="n"/>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C190" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D190" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E190" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3950,11 +4377,15 @@
       <c r="B191" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C191" s="6" t="n"/>
-      <c r="D191" s="6" t="n"/>
-      <c r="E191" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C191" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D191" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E191" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3970,10 +4401,12 @@
       <c r="C192" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="D192" s="6" t="n"/>
-      <c r="E192" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D192" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="E192" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -3989,10 +4422,12 @@
       <c r="C193" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="D193" s="6" t="n"/>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D193" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E193" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4005,11 +4440,15 @@
       <c r="B194" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C194" s="6" t="n"/>
-      <c r="D194" s="6" t="n"/>
-      <c r="E194" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C194" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D194" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4022,11 +4461,15 @@
       <c r="B195" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C195" s="6" t="n"/>
-      <c r="D195" s="6" t="n"/>
-      <c r="E195" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C195" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D195" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E195" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4039,11 +4482,15 @@
       <c r="B196" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6" t="n"/>
-      <c r="E196" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C196" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D196" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E196" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4059,10 +4506,12 @@
       <c r="C197" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="D197" s="6" t="n"/>
-      <c r="E197" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D197" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="E197" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4078,10 +4527,12 @@
       <c r="C198" s="5" t="n">
         <v>380</v>
       </c>
-      <c r="D198" s="6" t="n"/>
-      <c r="E198" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D198" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="E198" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4094,11 +4545,15 @@
       <c r="B199" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C199" s="6" t="n"/>
-      <c r="D199" s="6" t="n"/>
-      <c r="E199" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C199" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D199" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E199" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4114,10 +4569,12 @@
       <c r="C200" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D200" s="6" t="n"/>
-      <c r="E200" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D200" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E200" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4130,11 +4587,15 @@
       <c r="B201" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C201" s="6" t="n"/>
-      <c r="D201" s="6" t="n"/>
-      <c r="E201" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C201" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D201" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E201" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4147,11 +4608,15 @@
       <c r="B202" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C202" s="6" t="n"/>
-      <c r="D202" s="6" t="n"/>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C202" s="14" t="n">
+        <v>460</v>
+      </c>
+      <c r="D202" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="E202" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4646,15 @@
       <c r="B204" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C204" s="6" t="n"/>
-      <c r="D204" s="6" t="n"/>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C204" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D204" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E204" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4198,11 +4667,15 @@
       <c r="B205" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C205" s="6" t="n"/>
-      <c r="D205" s="6" t="n"/>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C205" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D205" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E205" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4215,11 +4688,15 @@
       <c r="B206" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C206" s="6" t="n"/>
-      <c r="D206" s="6" t="n"/>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C206" s="14" t="n">
+        <v>490</v>
+      </c>
+      <c r="D206" s="14" t="n">
+        <v>610</v>
+      </c>
+      <c r="E206" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4232,11 +4709,15 @@
       <c r="B207" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C207" s="6" t="n"/>
-      <c r="D207" s="6" t="n"/>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C207" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="D207" s="14" t="n">
+        <v>485</v>
+      </c>
+      <c r="E207" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4249,11 +4730,15 @@
       <c r="B208" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C208" s="6" t="n"/>
-      <c r="D208" s="6" t="n"/>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C208" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D208" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E208" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-0.5 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4266,11 +4751,15 @@
       <c r="B209" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C209" s="6" t="n"/>
-      <c r="D209" s="6" t="n"/>
-      <c r="E209" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C209" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D209" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="E209" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 1 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4283,11 +4772,15 @@
       <c r="B210" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C210" s="6" t="n"/>
-      <c r="D210" s="6" t="n"/>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C210" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D210" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E210" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4300,11 +4793,15 @@
       <c r="B211" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C211" s="6" t="n"/>
-      <c r="D211" s="6" t="n"/>
-      <c r="E211" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C211" s="14" t="n">
+        <v>460</v>
+      </c>
+      <c r="D211" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="E211" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4317,13 +4814,15 @@
       <c r="B212" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C212" s="6" t="n"/>
+      <c r="C212" s="14" t="n">
+        <v>270</v>
+      </c>
       <c r="D212" s="5" t="n">
         <v>333</v>
       </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>S not found</t>
+      <c r="E212" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = double ÷ 1.24</t>
         </is>
       </c>
     </row>
@@ -4336,11 +4835,15 @@
       <c r="B213" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6" t="n"/>
-      <c r="E213" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C213" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D213" s="14" t="n">
+        <v>365</v>
+      </c>
+      <c r="E213" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4353,11 +4856,15 @@
       <c r="B214" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C214" s="6" t="n"/>
-      <c r="D214" s="6" t="n"/>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C214" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="D214" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="E214" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1 routes with 2 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4373,14 +4880,12 @@
       <c r="C215" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="D215" s="5" t="inlineStr">
-        <is>
-          <t>Juhayna- Monofia</t>
-        </is>
-      </c>
-      <c r="E215" s="5" t="inlineStr">
-        <is>
-          <t>DD not found</t>
+      <c r="D215" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="E215" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4393,11 +4898,15 @@
       <c r="B216" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C216" s="6" t="n"/>
-      <c r="D216" s="6" t="n"/>
-      <c r="E216" s="5" t="inlineStr">
-        <is>
-          <t>not found</t>
+      <c r="C216" s="14" t="n">
+        <v>490</v>
+      </c>
+      <c r="D216" s="14" t="n">
+        <v>610</v>
+      </c>
+      <c r="E216" s="15" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED — single = median of weight-1.5 routes with 3 stop(s); double = single × 1.24</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4922,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -4422,14 +4931,14 @@
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TRUCK DRIVER MASTER</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Truck No (plate)</t>
@@ -5617,26 +6126,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="35.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>SPOT-RENT ROUTE MASTER</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Route Name</t>
@@ -5670,6 +6179,11 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Source</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Distance basis</t>
         </is>
       </c>
     </row>
@@ -5683,20 +6197,25 @@
         <v>204</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D4" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>3050</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>4350</v>
+      <c r="E4" s="16" t="n">
+        <v>4827.48</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>5730.18</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5710,20 +6229,25 @@
         <v>199</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D5" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="14" t="n">
         <v>160</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>5400</v>
+      <c r="E5" s="16" t="n">
+        <v>7304.36</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>7864.76</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5737,20 +6261,25 @@
         <v>197</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14" t="n">
         <v>490</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>8950</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>12900</v>
+      <c r="E6" s="16" t="n">
+        <v>9179.01</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>10122.45</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5764,20 +6293,25 @@
         <v>197</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D7" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="E7" s="8" t="n">
-        <v>3250</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>4650</v>
+      <c r="E7" s="16" t="n">
+        <v>7445.19</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>7894.96</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5791,20 +6325,25 @@
         <v>179</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>2050</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>2850</v>
+      <c r="E8" s="16" t="n">
+        <v>6580.71</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>7488.49</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5818,20 +6357,25 @@
         <v>160</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D9" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="14" t="n">
         <v>240</v>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>5050</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>7200</v>
+      <c r="E9" s="16" t="n">
+        <v>6605</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>8004.13</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5845,20 +6389,25 @@
         <v>158</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D10" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>3250</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>4650</v>
+      <c r="E10" s="16" t="n">
+        <v>6947.39</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>8094.71</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5872,20 +6421,25 @@
         <v>149</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="D11" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="14" t="n">
         <v>290</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>8350</v>
+      <c r="E11" s="16" t="n">
+        <v>6617.15</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>8208.540000000001</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5899,20 +6453,25 @@
         <v>134</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>5950</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>8550</v>
+      <c r="E12" s="16" t="n">
+        <v>7440.34</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>8466.35</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5926,20 +6485,25 @@
         <v>110</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>10850</v>
+      <c r="E13" s="16" t="n">
+        <v>7348.07</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>8436.16</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5953,20 +6517,25 @@
         <v>91</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>5950</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>8550</v>
+      <c r="E14" s="16" t="n">
+        <v>7348.07</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>8248.02</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -5980,20 +6549,25 @@
         <v>89</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14" t="n">
         <v>475</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>8750</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>12600</v>
+      <c r="E15" s="16" t="n">
+        <v>9179.01</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>10122.45</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6007,20 +6581,25 @@
         <v>85</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D16" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="14" t="n">
         <v>270</v>
       </c>
-      <c r="E16" s="8" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>7900</v>
+      <c r="E16" s="16" t="n">
+        <v>7649.17</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>8048.26</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6034,20 +6613,25 @@
         <v>84</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14" t="n">
         <v>515</v>
       </c>
-      <c r="E17" s="8" t="n">
-        <v>9350</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>13500</v>
+      <c r="E17" s="16" t="n">
+        <v>9179.01</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>10122.45</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6061,20 +6645,25 @@
         <v>78</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E18" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>10850</v>
+      <c r="E18" s="16" t="n">
+        <v>7751.16</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>9007.549999999999</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6088,20 +6677,25 @@
         <v>62</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>7450</v>
+      <c r="E19" s="16" t="n">
+        <v>6551.58</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>7867.09</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6115,20 +6709,25 @@
         <v>57</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>15450</v>
+      <c r="E20" s="16" t="n">
+        <v>9817.66</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>10610.23</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6142,20 +6741,25 @@
         <v>52</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>10850</v>
+      <c r="E21" s="16" t="n">
+        <v>8416.51</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>9551.059999999999</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6169,20 +6773,25 @@
         <v>49</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>10850</v>
+      <c r="E22" s="16" t="n">
+        <v>8564.65</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>9418.67</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6196,20 +6805,25 @@
         <v>49</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <v>6750</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>9750</v>
+      <c r="E23" s="16" t="n">
+        <v>7408.77</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>8519.77</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6223,20 +6837,25 @@
         <v>48</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>8710.34</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>8710.34</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -6250,20 +6869,25 @@
         <v>35</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>15450</v>
+      <c r="E25" s="16" t="n">
+        <v>9548.1</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>10851.8</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6277,20 +6901,25 @@
         <v>25</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>10850</v>
+      <c r="E26" s="16" t="n">
+        <v>7951.16</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>12100</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6304,20 +6933,25 @@
         <v>25</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E27" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>10850</v>
+      <c r="E27" s="16" t="n">
+        <v>11440.64</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>14292.98</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6331,9 +6965,9 @@
         <v>25</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14" t="n">
         <v>250</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -6344,7 +6978,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Estimated (alias) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6358,20 +6997,25 @@
         <v>22</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>525</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>9775.799999999999</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>11129.25</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -6385,20 +7029,25 @@
         <v>19</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D30" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="8" t="n">
-        <v>2050</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>2850</v>
+      <c r="E30" s="16" t="n">
+        <v>2879.97</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>4153.04</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6412,20 +7061,25 @@
         <v>18</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>7450</v>
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>625</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>11240.64</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>13439.32</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -6439,20 +7093,25 @@
         <v>17</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="D32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="14" t="n">
         <v>950</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <v>16250</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>23500</v>
+      <c r="E32" s="16" t="n">
+        <v>19356.09</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>21880.8</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6466,20 +7125,25 @@
         <v>16</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>860</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>14569.85</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>14500</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -6493,20 +7157,25 @@
         <v>16</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="14" t="n">
         <v>240</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>5050</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>7200</v>
+      <c r="F34" s="16" t="n">
+        <v>10268.8</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list (dry not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6520,20 +7189,25 @@
         <v>15</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E35" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>10850</v>
+      <c r="E35" s="16" t="n">
+        <v>10198.9</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>10948.9</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6547,20 +7221,25 @@
         <v>15</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14" t="n">
         <v>840</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>14500</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>20900</v>
+      <c r="E36" s="16" t="n">
+        <v>14278.45</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>15364.86</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6574,20 +7253,25 @@
         <v>14</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="E37" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>7450</v>
+      <c r="E37" s="16" t="n">
+        <v>6973.4</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>9384.77</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6601,9 +7285,9 @@
         <v>14</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D38" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="14" t="n">
         <v>250</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -6614,7 +7298,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Estimated (default 250km) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -6628,20 +7317,25 @@
         <v>13</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>15450</v>
+      <c r="E39" s="16" t="n">
+        <v>9548.1</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>11706.55</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6655,10 +7349,10 @@
         <v>12</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>178</v>
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>180</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>4050</v>
@@ -6668,7 +7362,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Estimated (alias) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6682,20 +7381,25 @@
         <v>12</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>8992.02</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>8191.62</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -6709,20 +7413,25 @@
         <v>12</v>
       </c>
       <c r="C42" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D42" s="14" t="n">
         <v>130</v>
       </c>
       <c r="E42" s="8" t="n">
         <v>3250</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>4650</v>
+      <c r="F42" s="16" t="n">
+        <v>8947.139999999999</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list (dry not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6736,20 +7445,25 @@
         <v>11</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E43" s="8" t="n">
-        <v>5950</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>8550</v>
+      <c r="E43" s="16" t="n">
+        <v>8910.34</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>9407.059999999999</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6763,20 +7477,25 @@
         <v>11</v>
       </c>
       <c r="C44" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>8992.02</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>10131.75</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -6790,20 +7509,25 @@
         <v>9</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D45" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D45" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>3250</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>4650</v>
+      <c r="E45" s="16" t="n">
+        <v>6780.71</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>8340.93</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6817,20 +7541,25 @@
         <v>8</v>
       </c>
       <c r="C46" s="8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D46" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>6750</v>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>9750</v>
+      <c r="E46" s="16" t="n">
+        <v>6817.15</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>9063.290000000001</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6844,20 +7573,25 @@
         <v>8</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="E47" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>7450</v>
+      <c r="E47" s="16" t="n">
+        <v>8910.34</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>9407.059999999999</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6871,9 +7605,9 @@
         <v>8</v>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D48" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D48" s="14" t="n">
         <v>1350</v>
       </c>
       <c r="E48" s="8" t="n">
@@ -6884,7 +7618,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6898,9 +7637,9 @@
         <v>7</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D49" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="14" t="n">
         <v>400</v>
       </c>
       <c r="E49" s="8" t="n">
@@ -6911,7 +7650,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6925,20 +7669,25 @@
         <v>7</v>
       </c>
       <c r="C50" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E50" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>10850</v>
+      <c r="E50" s="16" t="n">
+        <v>7548.07</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>9288.59</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -6952,20 +7701,25 @@
         <v>6</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>5200</v>
+        <v>1</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>875</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>14846.68</v>
       </c>
       <c r="F51" s="8" t="n">
         <v>7450</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -6979,20 +7733,25 @@
         <v>6</v>
       </c>
       <c r="C52" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E52" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>15450</v>
+      <c r="E52" s="16" t="n">
+        <v>9975.799999999999</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>11715</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7006,9 +7765,9 @@
         <v>5</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D53" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D53" s="14" t="n">
         <v>60</v>
       </c>
       <c r="E53" s="8" t="n">
@@ -7019,7 +7778,12 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7033,20 +7797,25 @@
         <v>5</v>
       </c>
       <c r="C54" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D54" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D54" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="E54" s="8" t="n">
-        <v>3250</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>4650</v>
+      <c r="E54" s="16" t="n">
+        <v>6817.15</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>9063.290000000001</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7060,20 +7829,25 @@
         <v>5</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>5400</v>
+        <v>1</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>535</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>9948.1</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>12558.99</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (geo 160 km implausible for rate)</t>
         </is>
       </c>
     </row>
@@ -7087,9 +7861,9 @@
         <v>5</v>
       </c>
       <c r="C56" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="14" t="n">
         <v>250</v>
       </c>
       <c r="E56" s="8" t="n">
@@ -7100,7 +7874,12 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7114,20 +7893,25 @@
         <v>4</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E57" s="8" t="n">
-        <v>5950</v>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>8550</v>
+      <c r="E57" s="16" t="n">
+        <v>7548.07</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>9100.459999999999</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7141,20 +7925,25 @@
         <v>4</v>
       </c>
       <c r="C58" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E58" s="8" t="n">
-        <v>7550</v>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>10850</v>
+      <c r="E58" s="16" t="n">
+        <v>8764.65</v>
+      </c>
+      <c r="F58" s="16" t="n">
+        <v>10268.8</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7168,20 +7957,25 @@
         <v>4</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D59" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D59" s="14" t="n">
         <v>1350</v>
       </c>
-      <c r="E59" s="8" t="n">
-        <v>22550</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>32650</v>
+      <c r="E59" s="16" t="n">
+        <v>21417.68</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>22560.68</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7195,20 +7989,25 @@
         <v>4</v>
       </c>
       <c r="C60" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>5200</v>
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>22500</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>7450</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -7222,20 +8021,25 @@
         <v>3</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>7450</v>
+        <v>1</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>7445.19</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>7795.08</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -7249,9 +8053,9 @@
         <v>3</v>
       </c>
       <c r="C62" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="14" t="n">
         <v>300</v>
       </c>
       <c r="E62" s="8" t="n">
@@ -7262,7 +8066,12 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Estimated (alias) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7276,20 +8085,25 @@
         <v>3</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="14" t="n">
         <v>515</v>
       </c>
-      <c r="E63" s="8" t="n">
-        <v>9350</v>
-      </c>
-      <c r="F63" s="8" t="n">
-        <v>13500</v>
+      <c r="E63" s="16" t="n">
+        <v>9379.01</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>10974.9</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7303,20 +8117,25 @@
         <v>3</v>
       </c>
       <c r="C64" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D64" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D64" s="14" t="n">
         <v>160</v>
       </c>
-      <c r="E64" s="8" t="n">
-        <v>3800</v>
+      <c r="E64" s="16" t="n">
+        <v>8500</v>
       </c>
       <c r="F64" s="8" t="n">
         <v>5400</v>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7330,20 +8149,25 @@
         <v>3</v>
       </c>
       <c r="C65" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E65" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F65" s="8" t="n">
-        <v>15450</v>
+      <c r="E65" s="16" t="n">
+        <v>10017.66</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>11462.67</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7357,20 +8181,25 @@
         <v>3</v>
       </c>
       <c r="C66" s="8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="14" t="n">
         <v>515</v>
       </c>
-      <c r="E66" s="8" t="n">
-        <v>9350</v>
-      </c>
-      <c r="F66" s="8" t="n">
-        <v>13500</v>
+      <c r="E66" s="16" t="n">
+        <v>9379.01</v>
+      </c>
+      <c r="F66" s="16" t="n">
+        <v>10974.9</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7384,9 +8213,9 @@
         <v>3</v>
       </c>
       <c r="C67" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="14" t="n">
         <v>400</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -7397,7 +8226,12 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7411,20 +8245,25 @@
         <v>2</v>
       </c>
       <c r="C68" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="14" t="n">
         <v>490</v>
       </c>
-      <c r="E68" s="8" t="n">
-        <v>8950</v>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>12900</v>
+      <c r="E68" s="16" t="n">
+        <v>9379.01</v>
+      </c>
+      <c r="F68" s="16" t="n">
+        <v>10974.9</v>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7438,9 +8277,9 @@
         <v>2</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D69" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D69" s="14" t="n">
         <v>350</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -7451,7 +8290,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7465,20 +8309,25 @@
         <v>2</v>
       </c>
       <c r="C70" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="E70" s="8" t="n">
-        <v>7550</v>
+      <c r="E70" s="16" t="n">
+        <v>4856.62</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>10850</v>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7491,10 +8340,10 @@
       <c r="B71" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D71" s="8" t="n">
+      <c r="C71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="14" t="n">
         <v>300</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -7505,7 +8354,12 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Estimated (alias) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7518,21 +8372,26 @@
       <c r="B72" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C72" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>5200</v>
+      <c r="C72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>7408.77</v>
       </c>
       <c r="F72" s="8" t="n">
         <v>7450</v>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -7545,10 +8404,10 @@
       <c r="B73" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D73" s="8" t="n">
+      <c r="C73" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="14" t="n">
         <v>160</v>
       </c>
       <c r="E73" s="8" t="n">
@@ -7559,7 +8418,12 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7572,21 +8436,26 @@
       <c r="B74" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C74" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>5200</v>
+      <c r="C74" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>505</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>9500</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>7450</v>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
@@ -7600,20 +8469,25 @@
         <v>2</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="14" t="n">
         <v>840</v>
       </c>
-      <c r="E75" s="8" t="n">
-        <v>14500</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>20900</v>
+      <c r="E75" s="16" t="n">
+        <v>14769.85</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>15353</v>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7626,10 +8500,10 @@
       <c r="B76" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D76" s="8" t="n">
+      <c r="C76" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="14" t="n">
         <v>240</v>
       </c>
       <c r="E76" s="8" t="n">
@@ -7640,7 +8514,12 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7654,9 +8533,9 @@
         <v>1</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D77" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D77" s="14" t="n">
         <v>400</v>
       </c>
       <c r="E77" s="8" t="n">
@@ -7667,7 +8546,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7681,20 +8565,25 @@
         <v>1</v>
       </c>
       <c r="C78" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>5950</v>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>8550</v>
+        <v>1</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>640</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>11440.64</v>
+      </c>
+      <c r="F78" s="16" t="n">
+        <v>14292.98</v>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (geo 300 km implausible for rate)</t>
         </is>
       </c>
     </row>
@@ -7708,20 +8597,25 @@
         <v>1</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="14" t="n">
         <v>840</v>
       </c>
-      <c r="E79" s="8" t="n">
-        <v>14500</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>20900</v>
+      <c r="E79" s="16" t="n">
+        <v>14478.45</v>
+      </c>
+      <c r="F79" s="16" t="n">
+        <v>16219.62</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H79" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7735,20 +8629,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>5200</v>
+        <v>1</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>6452.02</v>
       </c>
       <c r="F80" s="8" t="n">
         <v>7450</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Estimated (default 250km)</t>
+          <t>Price list (chilled not quoted — current kept)</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
         </is>
       </c>
     </row>
@@ -7762,9 +8661,9 @@
         <v>1</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D81" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="14" t="n">
         <v>130</v>
       </c>
       <c r="E81" s="8" t="n">
@@ -7775,7 +8674,12 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7789,9 +8693,9 @@
         <v>1</v>
       </c>
       <c r="C82" s="8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="14" t="n">
         <v>840</v>
       </c>
       <c r="E82" s="8" t="n">
@@ -7802,7 +8706,12 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7816,20 +8725,25 @@
         <v>1</v>
       </c>
       <c r="C83" s="8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="D83" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D83" s="14" t="n">
         <v>1100</v>
       </c>
-      <c r="E83" s="8" t="n">
-        <v>18600</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>26900</v>
+      <c r="E83" s="16" t="n">
+        <v>17211.85</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>18170.71</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7843,9 +8757,9 @@
         <v>1</v>
       </c>
       <c r="C84" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D84" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D84" s="14" t="n">
         <v>60</v>
       </c>
       <c r="E84" s="8" t="n">
@@ -7856,7 +8770,12 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7870,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="C85" s="8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>146</v>
+        <v>0.5</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>145</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>3550</v>
@@ -7883,7 +8802,12 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7897,20 +8821,25 @@
         <v>1</v>
       </c>
       <c r="C86" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D86" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="E86" s="8" t="n">
-        <v>10750</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>15450</v>
+      <c r="E86" s="16" t="n">
+        <v>9948.1</v>
+      </c>
+      <c r="F86" s="16" t="n">
+        <v>12558.99</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7924,20 +8853,25 @@
         <v>1</v>
       </c>
       <c r="C87" s="8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="D87" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D87" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="E87" s="8" t="n">
-        <v>32800</v>
-      </c>
-      <c r="F87" s="8" t="n">
-        <v>47500</v>
+      <c r="E87" s="16" t="n">
+        <v>28556.92</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>30241.94</v>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7951,9 +8885,9 @@
         <v>1</v>
       </c>
       <c r="C88" s="8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="14" t="n">
         <v>400</v>
       </c>
       <c r="E88" s="8" t="n">
@@ -7964,7 +8898,12 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -7978,9 +8917,9 @@
         <v>1</v>
       </c>
       <c r="C89" s="8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D89" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D89" s="14" t="n">
         <v>115</v>
       </c>
       <c r="E89" s="8" t="n">
@@ -7991,7 +8930,12 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -8005,9 +8949,9 @@
         <v>1</v>
       </c>
       <c r="C90" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="14" t="n">
         <v>490</v>
       </c>
       <c r="E90" s="8" t="n">
@@ -8018,7 +8962,12 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -8032,20 +8981,25 @@
         <v>1</v>
       </c>
       <c r="C91" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="14" t="n">
         <v>270</v>
       </c>
-      <c r="E91" s="8" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F91" s="8" t="n">
-        <v>7900</v>
+      <c r="E91" s="16" t="n">
+        <v>9975.799999999999</v>
+      </c>
+      <c r="F91" s="16" t="n">
+        <v>8786.25</v>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="H91" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -8059,9 +9013,9 @@
         <v>1</v>
       </c>
       <c r="C92" s="8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="14" t="n">
         <v>250</v>
       </c>
       <c r="E92" s="8" t="n">
@@ -8072,7 +9026,12 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Estimated (alias)</t>
+          <t>Estimated (alias) — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -8085,10 +9044,10 @@
       <c r="B93" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C93" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D93" s="8" t="n">
+      <c r="C93" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="14" t="n">
         <v>600</v>
       </c>
       <c r="E93" s="8" t="n">
@@ -8099,7 +9058,12 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H93" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
         </is>
       </c>
     </row>
@@ -8113,9 +9077,9 @@
         <v>1</v>
       </c>
       <c r="C94" s="8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D94" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D94" s="14" t="n">
         <v>115</v>
       </c>
       <c r="E94" s="8" t="n">
@@ -8126,11 +9090,376 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated — not in price list, current kept</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — geo estimate (dashboard engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EL- Tour</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>930</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>15606.73</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>15520.48</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H95" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Hurghada</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>990</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>16466.37</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>17397.26</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>From Menia to Dis El Sedeek</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H97" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Bani Swef-Menia- Dis El Sedeek</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="19" t="n">
+        <v>555</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>10175.8</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Factory to Dis EL Nada</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>24113.64</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H99" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Obour-Qalyobia</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>6817.15</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>9063.290000000001</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Eldaba- Matrouh</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>19556.09</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>22733.8</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H101" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Factory to Dis Abd Salam</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>6911.85</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>From Assiut to Dis TRINITY SOUTH</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H103" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — nearest-priced routes (median of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>From AUC to Mid Alex</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="19" t="n">
+        <v>635</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>12700</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H104" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AlexWest-MidAlex-Alex East</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>510</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>9579.01</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>11829.67</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H105" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AUC - Hurghada</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>16666.37</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>18254.35</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Factory to Dis Ehab Aram</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>1385</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>22158.49</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Price list (new route)</t>
+        </is>
+      </c>
+      <c r="H107" s="17" t="inlineStr">
+        <is>
+          <t>extrapolated — price model (long-haul fit)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8142,7 +9471,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -8153,14 +9482,14 @@
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>VENDOR MASTER</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Vendor (SvcPrvdr)</t>
